--- a/proyecto-asul/fase-07-oportunidades-soluciones/matriz-brechas.xlsx
+++ b/proyecto-asul/fase-07-oportunidades-soluciones/matriz-brechas.xlsx
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Cuenta compartida de Azure DevOps sin trazabilidad individual (licencia única entregada por el cliente)</t>
+          <t>Cuenta compartida de Jira (el sistema del cliente) sin trazabilidad individual (licencia única entregada por el cliente); en Azure DevOps cada persona de Asul ya tiene su propia cuenta individual</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -574,12 +574,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Bitácora de acceso compartido</t>
+          <t>Bitácora de acceso compartido (cuenta de Jira)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Es un control de proceso, no técnico: depende de la disciplina del equipo para registrarse; no elimina el riesgo de raíz (la cuenta sigue siendo compartida), solo mitiga el impacto si ocurre un incidente.</t>
+          <t>Es un control de proceso, no técnico: depende de la disciplina del equipo para registrarse; no elimina el riesgo de raíz (la cuenta de Jira sigue siendo compartida), solo mitiga el impacto si ocurre un incidente.</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Cuenta compartida sin trazabilidad (Fase 05); mejora parcial con la bitácora interna, no llega a 5 porque la cuenta sigue siendo técnicamente compartida</t>
+          <t>Cuenta de Jira compartida sin trazabilidad (Fase 05); mejora parcial con la bitácora interna, no llega a 5 porque la cuenta de Jira sigue siendo técnicamente compartida. En Azure DevOps no hay este problema: cada persona ya tiene su propia cuenta individual.</t>
         </is>
       </c>
     </row>
